--- a/Backtest/03-02-20/S&P500stock_03-02-20period252RS90.xlsx
+++ b/Backtest/03-02-20/S&P500stock_03-02-20period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Stock</t>
   </si>
@@ -130,100 +130,46 @@
     <t>NOW</t>
   </si>
   <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>EPAM</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>DAY</t>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>SBAC</t>
+  </si>
+  <si>
+    <t>PODD</t>
   </si>
   <si>
     <t>ENPH</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-05-01</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-04-23</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
+    <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>2020-05-05</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>REIT - Specialty</t>
   </si>
   <si>
     <t>Solar</t>
@@ -584,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -705,43 +651,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>90.42769857433809</v>
+        <v>91.03869653767821</v>
       </c>
       <c r="C2">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="D2">
-        <v>338.23</v>
+        <v>326.09</v>
       </c>
       <c r="E2">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="F2">
-        <v>0.4606252528832375</v>
+        <v>-0.6651618982058668</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="H2">
-        <v>0.09441475326904358</v>
+        <v>-0.5077175930382004</v>
       </c>
       <c r="I2">
-        <v>322.8919982910156</v>
+        <v>328.747998046875</v>
       </c>
       <c r="J2">
-        <v>308.2309997558594</v>
+        <v>342.7600006103515</v>
       </c>
       <c r="K2">
-        <v>290.3716015625</v>
+        <v>315.8650012207031</v>
       </c>
       <c r="L2">
-        <v>271.8170496368408</v>
+        <v>279.6358997344971</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="N2">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -762,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
@@ -771,7 +717,7 @@
         <v>213.99</v>
       </c>
       <c r="Y2">
-        <v>343.89</v>
+        <v>362.95</v>
       </c>
       <c r="Z2">
         <v>55.68</v>
@@ -798,16 +744,16 @@
         <v>-500</v>
       </c>
       <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>49</v>
       </c>
-      <c r="AI2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>62</v>
-      </c>
       <c r="AK2">
-        <v>90.27027027027026</v>
+        <v>90.41666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -815,43 +761,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>99.38900203665987</v>
+        <v>99.18533604887983</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>180.5</v>
       </c>
       <c r="D3">
-        <v>43.37</v>
+        <v>69</v>
       </c>
       <c r="E3">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="F3">
-        <v>2.05593924752241</v>
+        <v>-0.196538016036917</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="H3">
-        <v>1.369013922401127</v>
+        <v>-0.2320994711031773</v>
       </c>
       <c r="I3">
-        <v>39.96386642456055</v>
+        <v>70.68699951171875</v>
       </c>
       <c r="J3">
-        <v>35.5719331741333</v>
+        <v>66.39299983978272</v>
       </c>
       <c r="K3">
-        <v>29.01270664215088</v>
+        <v>60.69374984741211</v>
       </c>
       <c r="L3">
-        <v>19.45209669113159</v>
+        <v>45.3899374294281</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -863,61 +809,61 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>8.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
         <v>1</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
       <c r="X3">
-        <v>11.8</v>
+        <v>26.86</v>
       </c>
       <c r="Y3">
-        <v>43.53</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Z3">
-        <v>74.20999999999999</v>
+        <v>20.19</v>
       </c>
       <c r="AA3">
-        <v>114.77</v>
+        <v>-401.99</v>
       </c>
       <c r="AB3">
-        <v>49.99</v>
+        <v>163.79</v>
       </c>
       <c r="AC3">
-        <v>117.31</v>
+        <v>443.33</v>
       </c>
       <c r="AD3">
-        <v>1.77</v>
+        <v>10.5</v>
       </c>
       <c r="AE3">
-        <v>-11.26</v>
+        <v>106</v>
       </c>
       <c r="AF3">
-        <v>134.61</v>
+        <v>516.67</v>
       </c>
       <c r="AG3">
-        <v>43.65</v>
+        <v>60</v>
       </c>
       <c r="AH3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AI3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AJ3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>42.54195298149253</v>
+        <v>31.46987877888682</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -925,43 +871,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>93.89002036659878</v>
+        <v>95.92668024439919</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>427</v>
       </c>
       <c r="D4">
-        <v>17.34</v>
+        <v>265.09</v>
       </c>
       <c r="E4">
-        <v>0.8</v>
+        <v>2.55</v>
       </c>
       <c r="F4">
-        <v>-0.913953472057433</v>
+        <v>-0.4947532137807942</v>
       </c>
       <c r="G4">
+        <v>1.79</v>
+      </c>
+      <c r="H4">
+        <v>-0.5609070551660118</v>
+      </c>
+      <c r="I4">
+        <v>282.3720031738281</v>
+      </c>
+      <c r="J4">
+        <v>276.5175003051758</v>
+      </c>
+      <c r="K4">
+        <v>257.4509997558594</v>
+      </c>
+      <c r="L4">
+        <v>242.5622994232178</v>
+      </c>
+      <c r="M4">
         <v>1.02</v>
       </c>
-      <c r="H4">
-        <v>-0.7789217144696063</v>
-      </c>
-      <c r="I4">
-        <v>17.47544021606445</v>
-      </c>
-      <c r="J4">
-        <v>17.36442003250122</v>
-      </c>
-      <c r="K4">
-        <v>16.74986398696899</v>
-      </c>
-      <c r="L4">
-        <v>15.64973294258118</v>
-      </c>
-      <c r="M4">
-        <v>1.01</v>
-      </c>
       <c r="N4">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -979,55 +925,55 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>10.38</v>
+        <v>178.85</v>
       </c>
       <c r="Y4">
-        <v>17.77</v>
+        <v>309.85</v>
       </c>
       <c r="Z4">
-        <v>23.86</v>
+        <v>27.64</v>
       </c>
       <c r="AA4">
-        <v>39.02</v>
+        <v>-40.62</v>
       </c>
       <c r="AB4">
-        <v>41.04</v>
+        <v>103.12</v>
       </c>
       <c r="AC4">
-        <v>206.03</v>
+        <v>160.87</v>
       </c>
       <c r="AD4">
-        <v>6.08</v>
+        <v>-1.84</v>
       </c>
       <c r="AE4">
-        <v>8.23</v>
+        <v>215.79</v>
       </c>
       <c r="AF4">
-        <v>3.14</v>
+        <v>-32.14</v>
       </c>
       <c r="AG4">
-        <v>174.14</v>
+        <v>21.74</v>
       </c>
       <c r="AH4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="AK4">
-        <v>38.96755926764698</v>
+        <v>19.84560243299755</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1035,49 +981,49 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>91.64969450101833</v>
+        <v>99.59266802443992</v>
       </c>
       <c r="C5">
-        <v>318</v>
+        <v>393</v>
       </c>
       <c r="D5">
-        <v>517.46</v>
+        <v>189.97</v>
       </c>
       <c r="E5">
-        <v>1.46</v>
+        <v>2.86</v>
       </c>
       <c r="F5">
-        <v>-0.2517476629619276</v>
+        <v>-0.40670872682784</v>
       </c>
       <c r="G5">
-        <v>1.09</v>
+        <v>1.97</v>
       </c>
       <c r="H5">
-        <v>-0.6963088053591935</v>
+        <v>-0.4738697535023204</v>
       </c>
       <c r="I5">
-        <v>500.9200012207031</v>
+        <v>191.5539978027344</v>
       </c>
       <c r="J5">
-        <v>504.3670028686523</v>
+        <v>200.9614997863769</v>
       </c>
       <c r="K5">
-        <v>485.8705993652344</v>
+        <v>189.1127987670899</v>
       </c>
       <c r="L5">
-        <v>426.2163999938965</v>
+        <v>154.9160497283935</v>
       </c>
       <c r="M5">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="N5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1086,58 +1032,58 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>2.777777777777778</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>330.92</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="Y5">
-        <v>521.6900000000001</v>
+        <v>219.85</v>
       </c>
       <c r="Z5">
-        <v>108.55</v>
+        <v>10.67</v>
       </c>
       <c r="AA5">
-        <v>-21.05</v>
+        <v>-2.98</v>
       </c>
       <c r="AB5">
-        <v>18.38</v>
+        <v>46.15</v>
       </c>
       <c r="AC5">
-        <v>191.15</v>
+        <v>28.57</v>
       </c>
       <c r="AD5">
-        <v>2.12</v>
+        <v>6.59</v>
       </c>
       <c r="AE5">
-        <v>85.88</v>
+        <v>800</v>
       </c>
       <c r="AF5">
-        <v>25.53</v>
+        <v>-50</v>
       </c>
       <c r="AG5">
-        <v>24.78</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="AH5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AI5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="AJ5" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>33.6975462852792</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1145,772 +1091,109 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>99.18533604887983</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="D6">
-        <v>25.36</v>
+        <v>48.97</v>
       </c>
       <c r="E6">
-        <v>0.76</v>
+        <v>10.5</v>
       </c>
       <c r="F6">
-        <v>-0.9540871574571607</v>
+        <v>1.763161854851418</v>
       </c>
       <c r="G6">
-        <v>1.03</v>
+        <v>6.62</v>
       </c>
       <c r="H6">
-        <v>-0.7671198703109759</v>
+        <v>1.774593872809709</v>
       </c>
       <c r="I6">
-        <v>25.23699989318848</v>
+        <v>51.15199966430664</v>
       </c>
       <c r="J6">
-        <v>24.38625001907349</v>
+        <v>44.39349994659424</v>
       </c>
       <c r="K6">
-        <v>23.14425010681152</v>
+        <v>35.43400016784668</v>
       </c>
       <c r="L6">
-        <v>20.03932508468628</v>
+        <v>25.64975009441376</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
-      </c>
-      <c r="O6" t="s">
-        <v>48</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
       <c r="T6">
-        <v>7.777777777777777</v>
+        <v>5</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
       </c>
       <c r="X6">
-        <v>12.53</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Y6">
-        <v>26</v>
+        <v>59.15</v>
       </c>
       <c r="Z6">
-        <v>19.72</v>
+        <v>3.44</v>
       </c>
       <c r="AA6">
-        <v>262.15</v>
+        <v>-253.44</v>
       </c>
       <c r="AB6">
-        <v>19.84</v>
+        <v>1633.33</v>
       </c>
       <c r="AC6">
-        <v>64.91</v>
+        <v>3266.67</v>
       </c>
       <c r="AD6">
-        <v>11.32</v>
+        <v>42.86</v>
       </c>
       <c r="AE6">
-        <v>42.42</v>
+        <v>304</v>
       </c>
       <c r="AF6">
-        <v>-22.35</v>
+        <v>177.78</v>
       </c>
       <c r="AG6">
-        <v>49.12</v>
+        <v>200</v>
       </c>
       <c r="AH6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>66</v>
-      </c>
       <c r="AK6">
-        <v>32.78325064333477</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7">
-        <v>97.5560081466395</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
-      </c>
-      <c r="D7">
-        <v>402.38</v>
-      </c>
-      <c r="E7">
-        <v>1.13</v>
-      </c>
-      <c r="F7">
-        <v>-0.5828505675096805</v>
-      </c>
-      <c r="G7">
-        <v>1.65</v>
-      </c>
-      <c r="H7">
-        <v>-0.03540553247589098</v>
-      </c>
-      <c r="I7">
-        <v>406.8620056152344</v>
-      </c>
-      <c r="J7">
-        <v>402.8410003662109</v>
-      </c>
-      <c r="K7">
-        <v>380.1624005126953</v>
-      </c>
-      <c r="L7">
-        <v>333.0455499267578</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>1.07</v>
-      </c>
-      <c r="P7">
-        <v>2</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>224.45</v>
-      </c>
-      <c r="Y7">
-        <v>420.2</v>
-      </c>
-      <c r="Z7">
-        <v>11.3</v>
-      </c>
-      <c r="AA7">
-        <v>12.65</v>
-      </c>
-      <c r="AB7">
-        <v>25.26</v>
-      </c>
-      <c r="AC7">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>22.79</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>-14.48</v>
-      </c>
-      <c r="AG7">
-        <v>92.17</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK7">
-        <v>31.40318914349781</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8">
-        <v>92.66802443991853</v>
-      </c>
-      <c r="C8">
-        <v>485</v>
-      </c>
-      <c r="D8">
-        <v>228.14</v>
-      </c>
-      <c r="E8">
-        <v>1.36</v>
-      </c>
-      <c r="F8">
-        <v>-0.3520818764612464</v>
-      </c>
-      <c r="G8">
-        <v>1.59</v>
-      </c>
-      <c r="H8">
-        <v>-0.1062165974276732</v>
-      </c>
-      <c r="I8">
-        <v>230.7319976806641</v>
-      </c>
-      <c r="J8">
-        <v>227.069499206543</v>
-      </c>
-      <c r="K8">
-        <v>216.8289999389648</v>
-      </c>
-      <c r="L8">
-        <v>190.9678498840332</v>
-      </c>
-      <c r="M8">
-        <v>1.02</v>
-      </c>
-      <c r="N8">
-        <v>1.06</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>140.67</v>
-      </c>
-      <c r="Y8">
-        <v>236.04</v>
-      </c>
-      <c r="Z8">
-        <v>10.55</v>
-      </c>
-      <c r="AA8">
-        <v>25.58</v>
-      </c>
-      <c r="AB8">
-        <v>16.2</v>
-      </c>
-      <c r="AC8">
-        <v>9.91</v>
-      </c>
-      <c r="AD8">
-        <v>4.49</v>
-      </c>
-      <c r="AE8">
-        <v>14.02</v>
-      </c>
-      <c r="AF8">
-        <v>-4.46</v>
-      </c>
-      <c r="AG8">
-        <v>0.9</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK8">
-        <v>20.79981262372915</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>93.68635437881873</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>170.23</v>
-      </c>
-      <c r="E9">
-        <v>1.3</v>
-      </c>
-      <c r="F9">
-        <v>-0.4122824045608379</v>
-      </c>
-      <c r="G9">
-        <v>0.9</v>
-      </c>
-      <c r="H9">
-        <v>-0.9205438443731713</v>
-      </c>
-      <c r="I9">
-        <v>167.7579986572266</v>
-      </c>
-      <c r="J9">
-        <v>164.1679985046387</v>
-      </c>
-      <c r="K9">
-        <v>157.7557995605469</v>
-      </c>
-      <c r="L9">
-        <v>141.0252000427246</v>
-      </c>
-      <c r="M9">
-        <v>1.02</v>
-      </c>
-      <c r="N9">
-        <v>1.06</v>
-      </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="b">
-        <v>1</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>102.35</v>
-      </c>
-      <c r="Y9">
-        <v>174.05</v>
-      </c>
-      <c r="Z9">
-        <v>1212.87</v>
-      </c>
-      <c r="AA9">
-        <v>11.99</v>
-      </c>
-      <c r="AB9">
-        <v>5.26</v>
-      </c>
-      <c r="AC9">
-        <v>33.04</v>
-      </c>
-      <c r="AD9">
-        <v>10.58</v>
-      </c>
-      <c r="AE9">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="AF9">
-        <v>-18.6</v>
-      </c>
-      <c r="AG9">
-        <v>49.57</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK9">
-        <v>18.05959539829373</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10">
-        <v>97.75967413441956</v>
-      </c>
-      <c r="C10">
-        <v>123</v>
-      </c>
-      <c r="D10">
-        <v>61.07</v>
-      </c>
-      <c r="E10">
-        <v>1.51</v>
-      </c>
-      <c r="F10">
-        <v>-0.201580556212268</v>
-      </c>
-      <c r="G10">
-        <v>1.2</v>
-      </c>
-      <c r="H10">
-        <v>-0.5664885196142592</v>
-      </c>
-      <c r="I10">
-        <v>61.52799987792969</v>
-      </c>
-      <c r="J10">
-        <v>59.67049999237061</v>
-      </c>
-      <c r="K10">
-        <v>56.36139991760254</v>
-      </c>
-      <c r="L10">
-        <v>48.91575004577637</v>
-      </c>
-      <c r="M10">
-        <v>1.03</v>
-      </c>
-      <c r="N10">
-        <v>1.09</v>
-      </c>
-      <c r="P10">
-        <v>3</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>32.39</v>
-      </c>
-      <c r="Y10">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="Z10">
-        <v>37.82</v>
-      </c>
-      <c r="AA10">
-        <v>4.65</v>
-      </c>
-      <c r="AB10">
-        <v>1.68</v>
-      </c>
-      <c r="AC10">
-        <v>1.41</v>
-      </c>
-      <c r="AD10">
-        <v>6.52</v>
-      </c>
-      <c r="AE10">
-        <v>-37.39</v>
-      </c>
-      <c r="AF10">
-        <v>155.56</v>
-      </c>
-      <c r="AG10">
-        <v>-36.62</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK10">
-        <v>1.351351351351351</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11">
-        <v>97.35234215885947</v>
-      </c>
-      <c r="C11">
-        <v>355</v>
-      </c>
-      <c r="D11">
-        <v>73.29000000000001</v>
-      </c>
-      <c r="E11">
-        <v>1.19</v>
-      </c>
-      <c r="F11">
-        <v>-0.5226500394100889</v>
-      </c>
-      <c r="G11">
-        <v>1.78</v>
-      </c>
-      <c r="H11">
-        <v>0.1180184415863044</v>
-      </c>
-      <c r="I11">
-        <v>73.03200225830078</v>
-      </c>
-      <c r="J11">
-        <v>72.01850090026855</v>
-      </c>
-      <c r="K11">
-        <v>66.57160026550292</v>
-      </c>
-      <c r="L11">
-        <v>54.79980005264282</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.1</v>
-      </c>
-      <c r="P11">
-        <v>14</v>
-      </c>
-      <c r="Q11">
-        <v>6</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>3</v>
-      </c>
-      <c r="T11">
-        <v>20.55555555555555</v>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="b">
-        <v>1</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>40.37</v>
-      </c>
-      <c r="Y11">
-        <v>74.95</v>
-      </c>
-      <c r="Z11">
-        <v>7.36</v>
-      </c>
-      <c r="AA11">
-        <v>-13.71</v>
-      </c>
-      <c r="AB11">
-        <v>190</v>
-      </c>
-      <c r="AC11">
-        <v>2100</v>
-      </c>
-      <c r="AD11">
-        <v>3.38</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>-50</v>
-      </c>
-      <c r="AG11">
-        <v>300</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK11">
-        <v>69.91029607291614</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>131</v>
-      </c>
-      <c r="D12">
-        <v>31.52</v>
-      </c>
-      <c r="E12">
-        <v>3.38</v>
-      </c>
-      <c r="F12">
-        <v>1.674669236224998</v>
-      </c>
-      <c r="G12">
-        <v>3.62</v>
-      </c>
-      <c r="H12">
-        <v>2.289557766774299</v>
-      </c>
-      <c r="I12">
-        <v>31.95200119018555</v>
-      </c>
-      <c r="J12">
-        <v>31.15450048446655</v>
-      </c>
-      <c r="K12">
-        <v>26.8462003326416</v>
-      </c>
-      <c r="L12">
-        <v>22.49575010299683</v>
-      </c>
-      <c r="M12">
-        <v>1.03</v>
-      </c>
-      <c r="N12">
-        <v>1.19</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" t="b">
-        <v>0</v>
-      </c>
-      <c r="V12" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>6.6</v>
-      </c>
-      <c r="Y12">
-        <v>35.42</v>
-      </c>
-      <c r="Z12">
-        <v>2.97</v>
-      </c>
-      <c r="AA12">
-        <v>-112.43</v>
-      </c>
-      <c r="AB12">
-        <v>371.43</v>
-      </c>
-      <c r="AC12">
-        <v>2400</v>
-      </c>
-      <c r="AD12">
-        <v>20.42</v>
-      </c>
-      <c r="AE12">
-        <v>177.78</v>
-      </c>
-      <c r="AF12">
-        <v>200</v>
-      </c>
-      <c r="AG12">
-        <v>200</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK12">
-        <v>65.87490567854618</v>
+        <v>78.0390029598193</v>
       </c>
     </row>
   </sheetData>
